--- a/题库/PY选择题.xlsx
+++ b/题库/PY选择题.xlsx
@@ -1657,7 +1657,7 @@
         <rFont val="Segoe UI"/>
         <charset val="134"/>
       </rPr>
-      <t>”)</t>
+      <t>”))</t>
     </r>
   </si>
   <si>
@@ -1829,7 +1829,7 @@
 f.seek(0) 
 c=f.read(2) 
 print(c) 
-f.close0</t>
+f.close()</t>
     </r>
   </si>
   <si>
